--- a/DynamicChain46/DynamicChain46/Dump/DynamicChain46.xlsx
+++ b/DynamicChain46/DynamicChain46/Dump/DynamicChain46.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="275">
   <si>
     <t xml:space="preserve">Learn</t>
   </si>
@@ -175,6 +175,9 @@
     <t xml:space="preserve">Programming</t>
   </si>
   <si>
+    <t xml:space="preserve">Directive</t>
+  </si>
+  <si>
     <t xml:space="preserve">Document</t>
   </si>
   <si>
@@ -184,9 +187,15 @@
     <t xml:space="preserve">Transport</t>
   </si>
   <si>
+    <t xml:space="preserve">Cabinet</t>
+  </si>
+  <si>
     <t xml:space="preserve">Management</t>
   </si>
   <si>
+    <t xml:space="preserve">Application</t>
+  </si>
+  <si>
     <t xml:space="preserve">Diagram</t>
   </si>
   <si>
@@ -196,9 +205,15 @@
     <t xml:space="preserve">Commodity</t>
   </si>
   <si>
+    <t xml:space="preserve">Circuit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Engineering</t>
   </si>
   <si>
+    <t xml:space="preserve">Instruction</t>
+  </si>
+  <si>
     <t xml:space="preserve">Infographic</t>
   </si>
   <si>
@@ -208,9 +223,15 @@
     <t xml:space="preserve">Technology</t>
   </si>
   <si>
+    <t xml:space="preserve">Instrument</t>
+  </si>
+  <si>
     <t xml:space="preserve">Architecture</t>
   </si>
   <si>
+    <t xml:space="preserve">Differentiation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thesis</t>
   </si>
   <si>
@@ -220,9 +241,15 @@
     <t xml:space="preserve">Healthcare</t>
   </si>
   <si>
+    <t xml:space="preserve">Insulation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cultivation</t>
   </si>
   <si>
+    <t xml:space="preserve">Operation</t>
+  </si>
+  <si>
     <t xml:space="preserve">Research</t>
   </si>
   <si>
@@ -232,9 +259,15 @@
     <t xml:space="preserve">Agriculture</t>
   </si>
   <si>
+    <t xml:space="preserve">Component</t>
+  </si>
+  <si>
     <t xml:space="preserve">Development</t>
   </si>
   <si>
+    <t xml:space="preserve">Integration</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linguistic</t>
   </si>
   <si>
@@ -244,9 +277,15 @@
     <t xml:space="preserve">Handicraft</t>
   </si>
   <si>
+    <t xml:space="preserve">Accessory</t>
+  </si>
+  <si>
     <t xml:space="preserve">Economics</t>
   </si>
   <si>
+    <t xml:space="preserve">Ordinance</t>
+  </si>
+  <si>
     <t xml:space="preserve">Blog</t>
   </si>
   <si>
@@ -254,6 +293,9 @@
   </si>
   <si>
     <t xml:space="preserve">Textiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device</t>
   </si>
   <si>
     <t xml:space="preserve">Philosophy</t>
@@ -836,7 +878,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Courier New"/>
+      <name val="Cascadia Mono Light"/>
       <family val="3"/>
       <charset val="1"/>
     </font>
@@ -883,16 +925,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1023,7 +1061,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="20.46"/>
@@ -1031,7 +1069,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.15"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="11" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1198,774 +1236,755 @@
       <c r="A9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
+      </c>
+      <c r="I10" s="0"/>
+      <c r="J10" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="C11" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="C12" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="C13" s="1" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="C15" s="1" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+        <v>101</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" s="2"/>
+        <v>122</v>
+      </c>
       <c r="C20" s="1" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+        <v>125</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B21" s="2"/>
+        <v>126</v>
+      </c>
       <c r="C21" s="1" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+        <v>129</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B31" s="2"/>
+        <v>179</v>
+      </c>
       <c r="C31" s="1" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
+        <v>182</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B42" s="2"/>
+        <v>237</v>
+      </c>
       <c r="C42" s="1" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
+        <v>240</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/DynamicChain46/DynamicChain46/Dump/DynamicChain46.xlsx
+++ b/DynamicChain46/DynamicChain46/Dump/DynamicChain46.xlsx
@@ -193,27 +193,27 @@
     <t xml:space="preserve">Management</t>
   </si>
   <si>
+    <t xml:space="preserve">Instruction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commodity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engineering</t>
+  </si>
+  <si>
     <t xml:space="preserve">Application</t>
   </si>
   <si>
-    <t xml:space="preserve">Diagram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commodity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Circuit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instruction</t>
-  </si>
-  <si>
     <t xml:space="preserve">Infographic</t>
   </si>
   <si>
@@ -247,25 +247,25 @@
     <t xml:space="preserve">Cultivation</t>
   </si>
   <si>
+    <t xml:space="preserve">Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agriculture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development</t>
+  </si>
+  <si>
     <t xml:space="preserve">Operation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stamp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agriculture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration</t>
   </si>
   <si>
     <t xml:space="preserve">Linguistic</t>
@@ -925,12 +925,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1268,7 +1272,7 @@
       <c r="E10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I10" s="0"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="1" t="s">
         <v>61</v>
       </c>
@@ -1501,6 +1505,7 @@
       <c r="A22" s="1" t="s">
         <v>130</v>
       </c>
+      <c r="B22" s="0"/>
       <c r="C22" s="1" t="s">
         <v>131</v>
       </c>
@@ -1529,6 +1534,7 @@
       <c r="A24" s="1" t="s">
         <v>138</v>
       </c>
+      <c r="B24" s="0"/>
       <c r="C24" s="1" t="s">
         <v>139</v>
       </c>

--- a/DynamicChain46/DynamicChain46/Dump/DynamicChain46.xlsx
+++ b/DynamicChain46/DynamicChain46/Dump/DynamicChain46.xlsx
@@ -175,7 +175,7 @@
     <t xml:space="preserve">Programming</t>
   </si>
   <si>
-    <t xml:space="preserve">Directive</t>
+    <t xml:space="preserve">Framework</t>
   </si>
   <si>
     <t xml:space="preserve">Document</t>
@@ -193,7 +193,7 @@
     <t xml:space="preserve">Management</t>
   </si>
   <si>
-    <t xml:space="preserve">Instruction</t>
+    <t xml:space="preserve">Application</t>
   </si>
   <si>
     <t xml:space="preserve">Diagram</t>
@@ -211,7 +211,7 @@
     <t xml:space="preserve">Engineering</t>
   </si>
   <si>
-    <t xml:space="preserve">Application</t>
+    <t xml:space="preserve">Serialisation</t>
   </si>
   <si>
     <t xml:space="preserve">Infographic</t>
@@ -247,27 +247,27 @@
     <t xml:space="preserve">Cultivation</t>
   </si>
   <si>
+    <t xml:space="preserve">Deserialisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agriculture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development</t>
+  </si>
+  <si>
     <t xml:space="preserve">Integration</t>
   </si>
   <si>
-    <t xml:space="preserve">Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stamp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agriculture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linguistic</t>
   </si>
   <si>
@@ -277,13 +277,13 @@
     <t xml:space="preserve">Handicraft</t>
   </si>
   <si>
-    <t xml:space="preserve">Accessory</t>
+    <t xml:space="preserve">Accessories</t>
   </si>
   <si>
     <t xml:space="preserve">Economics</t>
   </si>
   <si>
-    <t xml:space="preserve">Ordinance</t>
+    <t xml:space="preserve">Terminal</t>
   </si>
   <si>
     <t xml:space="preserve">Blog</t>
@@ -1505,7 +1505,7 @@
       <c r="A22" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B22" s="0"/>
+      <c r="B22" s="2"/>
       <c r="C22" s="1" t="s">
         <v>131</v>
       </c>
@@ -1534,7 +1534,7 @@
       <c r="A24" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B24" s="0"/>
+      <c r="B24" s="2"/>
       <c r="C24" s="1" t="s">
         <v>139</v>
       </c>

--- a/DynamicChain46/DynamicChain46/Dump/DynamicChain46.xlsx
+++ b/DynamicChain46/DynamicChain46/Dump/DynamicChain46.xlsx
@@ -175,7 +175,7 @@
     <t xml:space="preserve">Programming</t>
   </si>
   <si>
-    <t xml:space="preserve">Framework</t>
+    <t xml:space="preserve">Virtual</t>
   </si>
   <si>
     <t xml:space="preserve">Document</t>
@@ -187,13 +187,13 @@
     <t xml:space="preserve">Transport</t>
   </si>
   <si>
-    <t xml:space="preserve">Cabinet</t>
+    <t xml:space="preserve">Device</t>
   </si>
   <si>
     <t xml:space="preserve">Management</t>
   </si>
   <si>
-    <t xml:space="preserve">Application</t>
+    <t xml:space="preserve">Pseudo</t>
   </si>
   <si>
     <t xml:space="preserve">Diagram</t>
@@ -211,7 +211,7 @@
     <t xml:space="preserve">Engineering</t>
   </si>
   <si>
-    <t xml:space="preserve">Serialisation</t>
+    <t xml:space="preserve">Digital</t>
   </si>
   <si>
     <t xml:space="preserve">Infographic</t>
@@ -223,13 +223,13 @@
     <t xml:space="preserve">Technology</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrument</t>
+    <t xml:space="preserve">Robot</t>
   </si>
   <si>
     <t xml:space="preserve">Architecture</t>
   </si>
   <si>
-    <t xml:space="preserve">Differentiation</t>
+    <t xml:space="preserve">Portal</t>
   </si>
   <si>
     <t xml:space="preserve">Thesis</t>
@@ -241,13 +241,13 @@
     <t xml:space="preserve">Healthcare</t>
   </si>
   <si>
-    <t xml:space="preserve">Insulation</t>
+    <t xml:space="preserve">Vault</t>
   </si>
   <si>
     <t xml:space="preserve">Cultivation</t>
   </si>
   <si>
-    <t xml:space="preserve">Deserialisation</t>
+    <t xml:space="preserve">Analogue</t>
   </si>
   <si>
     <t xml:space="preserve">Research</t>
@@ -259,27 +259,27 @@
     <t xml:space="preserve">Agriculture</t>
   </si>
   <si>
+    <t xml:space="preserve">Mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adhoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linguistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Handicraft</t>
+  </si>
+  <si>
     <t xml:space="preserve">Component</t>
   </si>
   <si>
-    <t xml:space="preserve">Development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linguistic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Handicraft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accessories</t>
-  </si>
-  <si>
     <t xml:space="preserve">Economics</t>
   </si>
   <si>
@@ -295,7 +295,7 @@
     <t xml:space="preserve">Textiles</t>
   </si>
   <si>
-    <t xml:space="preserve">Device</t>
+    <t xml:space="preserve">Console</t>
   </si>
   <si>
     <t xml:space="preserve">Philosophy</t>

--- a/DynamicChain46/DynamicChain46/Dump/DynamicChain46.xlsx
+++ b/DynamicChain46/DynamicChain46/Dump/DynamicChain46.xlsx
@@ -223,43 +223,43 @@
     <t xml:space="preserve">Technology</t>
   </si>
   <si>
+    <t xml:space="preserve">Mobile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Healthcare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cultivation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analogue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agriculture</t>
+  </si>
+  <si>
     <t xml:space="preserve">Robot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architecture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Healthcare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vault</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cultivation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analogue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stamp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agriculture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile</t>
   </si>
   <si>
     <t xml:space="preserve">Development</t>
